--- a/data/trans_orig/P20D1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>67,12%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>303</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>65881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>45380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>722</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>65833</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65881</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45380</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
